--- a/salesman_forms/014_sales_opportunity_tracker--salesman_forms.xlsx
+++ b/salesman_forms/014_sales_opportunity_tracker--salesman_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -994,7 +994,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sales Amount</t>
+          <t>Sales Amount Id</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lead Date</t>
+          <t>Lead Date Id</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Follow Up Date</t>
+          <t>Follow Up Date Id</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Close Date</t>
+          <t>Close Date Id</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes Id</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lead Source Category</t>
+          <t>Lead Source Category Id</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1130,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>qualification</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Decision</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>decision</t>
+          <t>closed_won</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Closed Won</t>
         </is>
       </c>
     </row>
@@ -1401,44 +1401,10 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>qualification</t>
+          <t>closed_lost</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>deal_stage_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>closed_won</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Closed Won</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>deal_stage_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>closed_lost</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
         <is>
           <t>Closed Lost</t>
         </is>
